--- a/assignments/원예작물학1_토마토_분석.xlsx
+++ b/assignments/원예작물학1_토마토_분석.xlsx
@@ -193,7 +193,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>그래프 1. 토마토 월평균 소매가격 추이(지역(확인 필요) vs 전국)</a:t>
+              <a:t>그래프 1. 토마토 월평균 소매가격 추이(대전 vs 전국)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -877,7 +877,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KAMIS 소매가격 일별 원자료 – 채소류, 토마토, 토마토, 상품, 1kg / 지역(확인 필요)</t>
+          <t>KAMIS 소매가격 일별 원자료 – 채소류, 토마토, 토마토, 상품, 1kg / 대전</t>
         </is>
       </c>
     </row>
@@ -21338,7 +21338,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>토마토 월평균 소매가격(지역(확인 필요))과 기상 비교 (2023년 10월~2026년 9월)</t>
+          <t>토마토 월평균 소매가격(대전)과 기상 비교 (2023년 10월~2026년 9월)</t>
         </is>
       </c>
     </row>
@@ -21368,7 +21368,7 @@
       <c r="D4" s="6" t="inlineStr">
         <is>
           <t>월평균 소매가격
-지역(확인 필요)(원/kg)</t>
+대전(원/kg)</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
